--- a/outputs/table/table1_baseline_characteristics_external.xlsx
+++ b/outputs/table/table1_baseline_characteristics_external.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="44">
   <si>
     <t>Characteristic</t>
   </si>
@@ -67,91 +67,85 @@
     <t>— Canon</t>
   </si>
   <si>
-    <t>61.3 ± 12.7</t>
+    <t>61.1 ± 12.2</t>
   </si>
   <si>
     <t>20–85</t>
   </si>
   <si>
-    <t>169.1 ± 6.3</t>
-  </si>
-  <si>
-    <t>68.0 ± 10.4</t>
-  </si>
-  <si>
-    <t>23.7 ± 3.1</t>
-  </si>
-  <si>
-    <t>217 (50.8%)</t>
-  </si>
-  <si>
-    <t>143 (33.5%)</t>
-  </si>
-  <si>
-    <t>97 (22.7%)</t>
-  </si>
-  <si>
-    <t>285 (66.7%)</t>
-  </si>
-  <si>
-    <t>88 (20.6%)</t>
-  </si>
-  <si>
-    <t>52 (12.2%)</t>
-  </si>
-  <si>
-    <t>2 (0.5%)</t>
-  </si>
-  <si>
-    <t>58.1 ± 12.4</t>
+    <t>169.9 ± 6.0</t>
+  </si>
+  <si>
+    <t>67.9 ± 9.0</t>
+  </si>
+  <si>
+    <t>23.5 ± 2.6</t>
+  </si>
+  <si>
+    <t>272 (49.7%)</t>
+  </si>
+  <si>
+    <t>179 (32.7%)</t>
+  </si>
+  <si>
+    <t>114 (20.8%)</t>
+  </si>
+  <si>
+    <t>329 (60.1%)</t>
+  </si>
+  <si>
+    <t>91 (16.6%)</t>
+  </si>
+  <si>
+    <t>13 (2.4%)</t>
+  </si>
+  <si>
+    <t>58.3 ± 12.2</t>
   </si>
   <si>
     <t>24–90</t>
   </si>
   <si>
-    <t>156.9 ± 5.8</t>
-  </si>
-  <si>
-    <t>56.5 ± 9.3</t>
-  </si>
-  <si>
-    <t>23.0 ± 3.6</t>
-  </si>
-  <si>
-    <t>208 (41.8%)</t>
-  </si>
-  <si>
-    <t>142 (28.5%)</t>
-  </si>
-  <si>
-    <t>71 (14.3%)</t>
-  </si>
-  <si>
-    <t>283 (56.8%)</t>
-  </si>
-  <si>
-    <t>131 (26.3%)</t>
-  </si>
-  <si>
-    <t>83 (16.7%)</t>
-  </si>
-  <si>
-    <t>1 (0.2%)</t>
+    <t>157.9 ± 5.4</t>
+  </si>
+  <si>
+    <t>57.0 ± 7.9</t>
+  </si>
+  <si>
+    <t>22.9 ± 3.1</t>
+  </si>
+  <si>
+    <t>235 (40.8%)</t>
+  </si>
+  <si>
+    <t>156 (27.1%)</t>
+  </si>
+  <si>
+    <t>74 (12.8%)</t>
+  </si>
+  <si>
+    <t>325 (56.4%)</t>
+  </si>
+  <si>
+    <t>126 (21.9%)</t>
+  </si>
+  <si>
+    <t>114 (19.8%)</t>
+  </si>
+  <si>
+    <t>11 (1.9%)</t>
   </si>
   <si>
     <t>&lt;0.001</t>
   </si>
   <si>
-    <t>0.007</t>
-  </si>
-  <si>
-    <t>0.118</t>
-  </si>
-  <si>
-    <t>0.001</t>
-  </si>
-  <si>
-    <t>0.015</t>
+    <t>0.003</t>
+  </si>
+  <si>
+    <t>0.046</t>
+  </si>
+  <si>
+    <t>0.165</t>
   </si>
 </sst>
 </file>
@@ -534,10 +528,10 @@
         <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -548,7 +542,7 @@
         <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -559,10 +553,10 @@
         <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -573,10 +567,10 @@
         <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -587,10 +581,10 @@
         <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -601,10 +595,10 @@
         <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -615,10 +609,10 @@
         <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -629,10 +623,10 @@
         <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D9" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -640,7 +634,7 @@
         <v>12</v>
       </c>
       <c r="D10" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -651,7 +645,7 @@
         <v>25</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -662,7 +656,7 @@
         <v>26</v>
       </c>
       <c r="C12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -670,10 +664,10 @@
         <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -681,10 +675,10 @@
         <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
